--- a/data/reports/mapping_oracle_full.xlsx
+++ b/data/reports/mapping_oracle_full.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched Client Columns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjudication Queue" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapeamentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados da Execução" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colunas do Cliente sem Uso" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fila de Revisão" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,127 +434,127 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>model_column_number</t>
+          <t>numero_coluna_modelo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>model_column</t>
+          <t>coluna_modelo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>client_column_number</t>
+          <t>numero_coluna_cliente</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>client_column</t>
+          <t>coluna_cliente</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>name_confidence</t>
+          <t>confianca_nome</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>name_runner_up_confidence</t>
+          <t>confianca_nome_segunda_melhor</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>name_margin</t>
+          <t>margem_nome</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>data_confidence</t>
+          <t>confianca_dados</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>final_confidence</t>
+          <t>confianca_final</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>metodo</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>situacao</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>justificativa</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>catalog_name</t>
+          <t>nome_catalogo</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>catalog_coverage</t>
+          <t>cobertura_catalogo</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>catalog_distinct_coverage</t>
+          <t>cobertura_distinta_catalogo</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>catalog_confidence</t>
+          <t>confianca_catalogo</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>decided_by</t>
+          <t>decidido_por</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>supported_by</t>
+          <t>apoiado_por</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>vetoed_by</t>
+          <t>vetado_por</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>arithmetic_proof</t>
+          <t>prova_aritmetica</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>llm_data_confidence</t>
+          <t>confianca_dados_ia</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>llm_final_confidence</t>
+          <t>confianca_final_ia</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>reviewer_status</t>
+          <t>parecer_revisor</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>correct_client_column</t>
+          <t>coluna_cliente_correta</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>reviewer_note</t>
+          <t>observacao_revisor</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U23" t="n">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U30" t="n">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U31" t="n">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -2099,27 +2099,27 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -2158,17 +2158,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>catalogo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Versioned official cfop codes cover 88.2% of the 17 distinct codes used (66.7% of rows) and uniquely identify this candidate among the available columns.</t>
+          <t>A tabela oficial versionada de CFOP cobre 88,2% dos 17 códigos distintos usados (66,7% das linhas) e identifica este candidato de forma única entre as colunas disponíveis.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>catalogo</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>semantic + catalog</t>
+          <t>semantico + catalogo</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -2285,17 +2285,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U37" t="n">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U38" t="n">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -2539,33 +2539,33 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
+          <t>valor = base x alíquota se confirma para ICMS em 2540 linhas, com aderência 1,0</t>
         </is>
       </c>
     </row>
@@ -2600,33 +2600,33 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
+          <t>valor = base x alíquota se confirma para ICMS em 2540 linhas, com aderência 1,0</t>
         </is>
       </c>
     </row>
@@ -2664,27 +2664,27 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2929,33 +2929,33 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
+          <t>valor = base x alíquota se confirma para IPI em 333 linhas, com aderência 1,0</t>
         </is>
       </c>
     </row>
@@ -2990,33 +2990,33 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
+          <t>valor = base x alíquota se confirma para IPI em 333 linhas, com aderência 1,0</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
@@ -3181,27 +3181,27 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
@@ -3237,27 +3237,27 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -3293,27 +3293,27 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
@@ -3349,27 +3349,27 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3584,17 +3584,17 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U61" t="n">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S62" t="inlineStr"/>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U63" t="n">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U66" t="n">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S67" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4193,17 +4193,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U73" t="n">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U78" t="n">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S79" t="inlineStr"/>
@@ -4561,12 +4561,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U81" t="n">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U83" t="n">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U86" t="n">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S87" t="inlineStr"/>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S88" t="inlineStr"/>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U106" t="n">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5898,17 +5898,17 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U108" t="n">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6220,17 +6220,17 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U115" t="n">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6412,27 +6412,27 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The strongest header candidate has weak row evidence; preserve the name-based mapping for review instead of replacing it with a merely similar value shape.</t>
+          <t>O candidato com o cabeçalho mais forte tem evidência fraca nas linhas; o mapeamento por nome é mantido para revisão, em vez de ser trocado por uma coluna que só tem formato de valores parecido.</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6607,12 +6607,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -6975,12 +6975,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7113,12 +7113,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U136" t="n">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -7389,17 +7389,17 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U140" t="n">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U141" t="n">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U147" t="n">
@@ -7757,17 +7757,17 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U148" t="n">
@@ -7803,17 +7803,17 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U149" t="n">
@@ -7849,17 +7849,17 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U150" t="n">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -7987,17 +7987,17 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U153" t="n">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -8171,17 +8171,17 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U157" t="n">
@@ -8217,17 +8217,17 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U158" t="n">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S159" t="inlineStr"/>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -8466,12 +8466,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -8612,12 +8612,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S166" t="inlineStr"/>
@@ -8677,12 +8677,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S167" t="inlineStr"/>
@@ -8734,17 +8734,17 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U168" t="n">
@@ -8780,17 +8780,17 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U169" t="n">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S175" t="inlineStr"/>
@@ -9129,12 +9129,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S176" t="inlineStr"/>
@@ -9186,12 +9186,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -9301,12 +9301,12 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S179" t="inlineStr"/>
@@ -9343,17 +9343,17 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U180" t="n">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S181" t="inlineStr"/>
@@ -9454,12 +9454,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -9500,17 +9500,17 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U183" t="n">
@@ -9546,17 +9546,17 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U184" t="n">
@@ -9597,27 +9597,27 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S185" t="inlineStr"/>
@@ -9648,17 +9648,17 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U186" t="n">
@@ -9694,17 +9694,17 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U187" t="n">
@@ -9748,27 +9748,27 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S188" t="inlineStr"/>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S189" t="inlineStr"/>
@@ -9870,12 +9870,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -9921,33 +9921,33 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr">
         <is>
-          <t>valor = base x aliquota holds for icms on 2540 rows at fit 1.0</t>
+          <t>valor = base x alíquota se confirma para ICMS em 2540 linhas, com aderência 1,0</t>
         </is>
       </c>
     </row>
@@ -9977,17 +9977,17 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U192" t="n">
@@ -10028,33 +10028,33 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr">
         <is>
-          <t>valor = base x aliquota holds for ipi on 333 rows at fit 1.0</t>
+          <t>valor = base x alíquota se confirma para IPI em 333 linhas, com aderência 1,0</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S194" t="inlineStr"/>
@@ -10157,12 +10157,12 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S195" t="inlineStr"/>
@@ -10222,12 +10222,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S196" t="inlineStr"/>
@@ -10279,17 +10279,17 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U197" t="n">
@@ -10325,17 +10325,17 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U198" t="n">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S199" t="inlineStr"/>
@@ -10441,27 +10441,27 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S200" t="inlineStr"/>
@@ -10492,17 +10492,17 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U201" t="n">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -10630,17 +10630,17 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U204" t="n">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -10730,27 +10730,27 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S206" t="inlineStr"/>
@@ -10795,12 +10795,12 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S207" t="inlineStr"/>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U208" t="n">
@@ -10898,12 +10898,12 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -10967,12 +10967,12 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S210" t="inlineStr"/>
@@ -11017,12 +11017,12 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S211" t="inlineStr"/>
@@ -11074,17 +11074,17 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U212" t="n">
@@ -11120,12 +11120,12 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -11171,27 +11171,27 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S214" t="inlineStr"/>
@@ -11222,17 +11222,17 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U215" t="n">
@@ -11276,12 +11276,12 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S216" t="inlineStr"/>
@@ -11341,12 +11341,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -11356,12 +11356,12 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S217" t="inlineStr"/>
@@ -11398,17 +11398,17 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U218" t="n">
@@ -11444,12 +11444,12 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -11495,17 +11495,17 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>semantic + catalog (agrees)</t>
+          <t>semantico + catalogo (concorda)</t>
         </is>
       </c>
       <c r="S220" t="inlineStr"/>
@@ -11565,17 +11565,17 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>semantic + catalog (agrees)</t>
+          <t>semantico + catalogo (concorda)</t>
         </is>
       </c>
       <c r="S221" t="inlineStr"/>
@@ -11635,17 +11635,17 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>semantic + catalog (agrees)</t>
+          <t>semantico + catalogo (concorda)</t>
         </is>
       </c>
       <c r="S222" t="inlineStr"/>
@@ -11705,17 +11705,17 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>semantic + catalog (agrees)</t>
+          <t>semantico + catalogo (concorda)</t>
         </is>
       </c>
       <c r="S223" t="inlineStr"/>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -11908,17 +11908,17 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U227" t="n">
@@ -11954,17 +11954,17 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="U228" t="n">
@@ -11985,35 +11985,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chave</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mapping_schema_version</t>
+          <t>versao_esquema_mapeamento</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generated_at_utc</t>
+          <t>gerado_em_utc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12025,7 +12025,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prompt_version</t>
+          <t>versao_prompt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12037,7 +12037,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>client_file</t>
+          <t>arquivo_cliente</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12049,7 +12049,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>client_sha256</t>
+          <t>sha256_cliente</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12061,7 +12061,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>model_file</t>
+          <t>arquivo_modelo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12073,7 +12073,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model_sha256</t>
+          <t>sha256_modelo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12085,7 +12085,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>client_sheet</t>
+          <t>aba_cliente</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12097,7 +12097,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>model_sheet</t>
+          <t>aba_modelo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12109,7 +12109,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>client_header_row</t>
+          <t>linha_cabecalho_cliente</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -12119,7 +12119,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_header_row</t>
+          <t>linha_cabecalho_modelo</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -12129,7 +12129,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>embedding_model</t>
+          <t>modelo_embedding</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -12141,7 +12141,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llm_model</t>
+          <t>modelo_ia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -12153,7 +12153,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>name_threshold</t>
+          <t>limiar_nome</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -12163,7 +12163,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>name_margin</t>
+          <t>margem_minima_nome</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -12173,7 +12173,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>final_threshold</t>
+          <t>limiar_final</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -12183,7 +12183,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>candidate_count</t>
+          <t>quantidade_candidatos</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -12193,7 +12193,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sample_size</t>
+          <t>tamanho_amostra</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -12203,13 +12203,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>reference_manifest_sha256</t>
+          <t>sha256_manifesto_referencia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>c4e2106d5da8d59bb0b3ba304cd6c68500a22be3972e6bce81c122fc29a677f1</t>
         </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>migrado_da_versao_esquema</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -12229,52 +12239,52 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>client_column_number</t>
+          <t>numero_coluna_cliente</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>client_column</t>
+          <t>coluna_cliente</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>disposicao</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>review_priority</t>
+          <t>prioridade_revisao</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>rows_with_value</t>
+          <t>linhas_com_valor</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>distinct_values</t>
+          <t>valores_distintos</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>signals</t>
+          <t>sinais</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>signal_detail</t>
+          <t>detalhe_sinais</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>closest_model_column</t>
+          <t>coluna_modelo_mais_proxima</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>closest_name_confidence</t>
+          <t>confianca_nome_mais_proxima</t>
         </is>
       </c>
     </row>
@@ -12289,12 +12299,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -12305,12 +12315,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>data</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>holds dates</t>
+          <t>contém datas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -12333,12 +12343,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -12349,7 +12359,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -12372,12 +12382,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -12388,7 +12398,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -12411,12 +12421,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -12427,7 +12437,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12450,12 +12460,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -12466,7 +12476,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -12489,12 +12499,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -12505,7 +12515,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -12528,12 +12538,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -12544,7 +12554,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -12567,12 +12577,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -12583,12 +12593,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>catalogo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>88.2% of its 17 distinct codes are valid cfop</t>
+          <t>88,2% dos seus 17 códigos distintos são válidos na tabela oficial de CFOP</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12611,12 +12621,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -12627,7 +12637,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -12650,12 +12660,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -12666,7 +12676,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -12689,12 +12699,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -12705,7 +12715,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -12728,12 +12738,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -12744,7 +12754,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -12767,12 +12777,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -12783,7 +12793,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -12806,12 +12816,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>proposed_not_accepted</t>
+          <t>proposta_nao_aceita</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>shortlist</t>
+          <t>prioritaria</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -12822,7 +12832,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -12845,12 +12855,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -12861,7 +12871,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -12884,12 +12894,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -12900,7 +12910,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -12923,12 +12933,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -12939,7 +12949,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12962,12 +12972,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -12978,7 +12988,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -13001,12 +13011,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -13017,7 +13027,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -13040,12 +13050,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -13056,7 +13066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No values in this column.</t>
+          <t>Esta coluna não tem valores.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -13079,12 +13089,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -13095,7 +13105,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -13118,12 +13128,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -13134,7 +13144,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -13157,12 +13167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -13173,7 +13183,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -13196,12 +13206,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -13212,7 +13222,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -13235,12 +13245,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -13251,7 +13261,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -13274,12 +13284,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -13290,7 +13300,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13313,12 +13323,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -13329,7 +13339,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13352,12 +13362,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -13368,7 +13378,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -13391,12 +13401,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -13407,7 +13417,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -13430,12 +13440,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>never_referenced</t>
+          <t>nunca_referenciada</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -13446,7 +13456,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Carries data, but no signal matched. Listed for completeness.</t>
+          <t>Contém dados, mas nenhum sinal foi identificado. Listada apenas para que a relação fique completa.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -13475,67 +13485,67 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>posicao</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>model_column_number</t>
+          <t>numero_coluna_modelo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>model_column</t>
+          <t>coluna_modelo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>proposed_client_column_number</t>
+          <t>numero_coluna_cliente_proposta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>proposed_client_column</t>
+          <t>coluna_cliente_proposta</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>final_confidence</t>
+          <t>confianca_final</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>gate_distance</t>
+          <t>distancia_limiar</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>name_margin</t>
+          <t>margem_nome</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>rows_with_value</t>
+          <t>linhas_com_valor</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>resolver_disagrees</t>
+          <t>divergencia_ia</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>arithmetic_proof</t>
+          <t>prova_aritmetica</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>client_sample_values</t>
+          <t>amostra_valores_cliente</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>why_held</t>
+          <t>motivo_retencao</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13588,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>name evidence only - this branch cannot auto-accept however well the headers match</t>
+          <t>só há evidência de nome - este caminho não aceita automaticamente, por mais que os cabeçalhos coincidam</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13631,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>name evidence only - this branch cannot auto-accept however well the headers match</t>
+          <t>só há evidência de nome - este caminho não aceita automaticamente, por mais que os cabeçalhos coincidam</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13717,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13760,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13803,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13846,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13889,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13932,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13970,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>resolver scored it 0.1</t>
+          <t>o resolvedor de IA atribuiu confiança 0,1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -13970,7 +13980,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14023,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14066,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14109,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14152,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14195,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14238,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14281,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14324,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14367,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14410,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14443,7 +14453,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14491,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>resolver scored it 0.0</t>
+          <t>o resolvedor de IA atribuiu confiança 0,0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -14491,7 +14501,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14544,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14577,7 +14587,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14630,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14668,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>resolver scored it 0.0</t>
+          <t>o resolvedor de IA atribuiu confiança 0,0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -14668,7 +14678,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14721,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14754,7 +14764,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14802,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>resolver scored it 0.5</t>
+          <t>o resolvedor de IA atribuiu confiança 0,5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -14802,7 +14812,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14850,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>resolver scored it 0.0</t>
+          <t>o resolvedor de IA atribuiu confiança 0,0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -14850,7 +14860,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14893,7 +14903,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14946,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -14979,7 +14989,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15032,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15070,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>resolver scored it 0.0</t>
+          <t>o resolvedor de IA atribuiu confiança 0,0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -15070,7 +15080,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15123,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15166,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>below the accept threshold</t>
+          <t>abaixo do limiar de aceite</t>
         </is>
       </c>
     </row>
